--- a/속초고등학교 교사 명단.xlsx
+++ b/속초고등학교 교사 명단.xlsx
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="13.6640625" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -1079,34 +1079,34 @@
       </c>
     </row>
     <row r="2" hidden="1" s="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>교장</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>교장</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>장승복</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>교감</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>교감</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>설태수</t>
         </is>
@@ -1997,6 +1997,24 @@
           <t>한철우</t>
         </is>
       </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>게스트</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>이병천</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D50">
